--- a/artfynd/A 26375-2022 artfynd.xlsx
+++ b/artfynd/A 26375-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121556504</v>
+        <v>121556501</v>
       </c>
       <c r="B2" t="n">
-        <v>90936</v>
+        <v>5192</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1101</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402892</v>
+        <v>402640</v>
       </c>
       <c r="R2" t="n">
-        <v>6303180</v>
+        <v>6302988</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121556526</v>
+        <v>121556527</v>
       </c>
       <c r="B3" t="n">
-        <v>5192</v>
+        <v>96371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403015</v>
+        <v>402956</v>
       </c>
       <c r="R3" t="n">
-        <v>6303353</v>
+        <v>6303292</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121556501</v>
+        <v>121556526</v>
       </c>
       <c r="B4" t="n">
         <v>5192</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402640</v>
+        <v>403015</v>
       </c>
       <c r="R4" t="n">
-        <v>6302988</v>
+        <v>6303353</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121556527</v>
+        <v>121556504</v>
       </c>
       <c r="B5" t="n">
-        <v>96371</v>
+        <v>90936</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>1101</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>402956</v>
+        <v>402892</v>
       </c>
       <c r="R5" t="n">
-        <v>6303292</v>
+        <v>6303180</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 26375-2022 artfynd.xlsx
+++ b/artfynd/A 26375-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121556501</v>
+        <v>121556527</v>
       </c>
       <c r="B2" t="n">
-        <v>5192</v>
+        <v>96372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402640</v>
+        <v>402956</v>
       </c>
       <c r="R2" t="n">
-        <v>6302988</v>
+        <v>6303292</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121556527</v>
+        <v>121556504</v>
       </c>
       <c r="B3" t="n">
-        <v>96371</v>
+        <v>90937</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>1101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402956</v>
+        <v>402892</v>
       </c>
       <c r="R3" t="n">
-        <v>6303292</v>
+        <v>6303180</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121556526</v>
+        <v>121556501</v>
       </c>
       <c r="B4" t="n">
         <v>5192</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403015</v>
+        <v>402640</v>
       </c>
       <c r="R4" t="n">
-        <v>6303353</v>
+        <v>6302988</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121556504</v>
+        <v>121556505</v>
       </c>
       <c r="B5" t="n">
-        <v>90936</v>
+        <v>96372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1101</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>402892</v>
+        <v>402925</v>
       </c>
       <c r="R5" t="n">
-        <v>6303180</v>
+        <v>6303306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121556505</v>
+        <v>121556526</v>
       </c>
       <c r="B6" t="n">
-        <v>96371</v>
+        <v>5192</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>402925</v>
+        <v>403015</v>
       </c>
       <c r="R6" t="n">
-        <v>6303306</v>
+        <v>6303353</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 26375-2022 artfynd.xlsx
+++ b/artfynd/A 26375-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121556527</v>
+        <v>121556526</v>
       </c>
       <c r="B2" t="n">
-        <v>96372</v>
+        <v>5192</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402956</v>
+        <v>403015</v>
       </c>
       <c r="R2" t="n">
-        <v>6303292</v>
+        <v>6303353</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121556504</v>
+        <v>121556505</v>
       </c>
       <c r="B3" t="n">
-        <v>90937</v>
+        <v>96372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1101</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402892</v>
+        <v>402925</v>
       </c>
       <c r="R3" t="n">
-        <v>6303180</v>
+        <v>6303306</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121556501</v>
+        <v>121556504</v>
       </c>
       <c r="B4" t="n">
-        <v>5192</v>
+        <v>90937</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>1101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402640</v>
+        <v>402892</v>
       </c>
       <c r="R4" t="n">
-        <v>6302988</v>
+        <v>6303180</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121556505</v>
+        <v>121556527</v>
       </c>
       <c r="B5" t="n">
         <v>96372</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>402925</v>
+        <v>402956</v>
       </c>
       <c r="R5" t="n">
-        <v>6303306</v>
+        <v>6303292</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121556526</v>
+        <v>121556501</v>
       </c>
       <c r="B6" t="n">
         <v>5192</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>403015</v>
+        <v>402640</v>
       </c>
       <c r="R6" t="n">
-        <v>6303353</v>
+        <v>6302988</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 26375-2022 artfynd.xlsx
+++ b/artfynd/A 26375-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121556526</v>
+        <v>121556501</v>
       </c>
       <c r="B2" t="n">
         <v>5192</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>403015</v>
+        <v>402640</v>
       </c>
       <c r="R2" t="n">
-        <v>6303353</v>
+        <v>6302988</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121556505</v>
+        <v>121556527</v>
       </c>
       <c r="B3" t="n">
         <v>96372</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402925</v>
+        <v>402956</v>
       </c>
       <c r="R3" t="n">
-        <v>6303306</v>
+        <v>6303292</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121556504</v>
+        <v>121556505</v>
       </c>
       <c r="B4" t="n">
-        <v>90937</v>
+        <v>96372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1101</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402892</v>
+        <v>402925</v>
       </c>
       <c r="R4" t="n">
-        <v>6303180</v>
+        <v>6303306</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121556527</v>
+        <v>121556504</v>
       </c>
       <c r="B5" t="n">
-        <v>96372</v>
+        <v>90937</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>1101</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>402956</v>
+        <v>402892</v>
       </c>
       <c r="R5" t="n">
-        <v>6303292</v>
+        <v>6303180</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121556501</v>
+        <v>121556526</v>
       </c>
       <c r="B6" t="n">
         <v>5192</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>402640</v>
+        <v>403015</v>
       </c>
       <c r="R6" t="n">
-        <v>6302988</v>
+        <v>6303353</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 26375-2022 artfynd.xlsx
+++ b/artfynd/A 26375-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121556501</v>
+        <v>121556526</v>
       </c>
       <c r="B2" t="n">
         <v>5192</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402640</v>
+        <v>403015</v>
       </c>
       <c r="R2" t="n">
-        <v>6302988</v>
+        <v>6303353</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121556527</v>
+        <v>121556504</v>
       </c>
       <c r="B3" t="n">
-        <v>96372</v>
+        <v>90937</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>1101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402956</v>
+        <v>402892</v>
       </c>
       <c r="R3" t="n">
-        <v>6303292</v>
+        <v>6303180</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121556504</v>
+        <v>121556501</v>
       </c>
       <c r="B5" t="n">
-        <v>90937</v>
+        <v>5192</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1101</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>402892</v>
+        <v>402640</v>
       </c>
       <c r="R5" t="n">
-        <v>6303180</v>
+        <v>6302988</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121556526</v>
+        <v>121556527</v>
       </c>
       <c r="B6" t="n">
-        <v>5192</v>
+        <v>96372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>403015</v>
+        <v>402956</v>
       </c>
       <c r="R6" t="n">
-        <v>6303353</v>
+        <v>6303292</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 26375-2022 artfynd.xlsx
+++ b/artfynd/A 26375-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121556526</v>
+        <v>121556527</v>
       </c>
       <c r="B2" t="n">
-        <v>5192</v>
+        <v>96380</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>403015</v>
+        <v>402956</v>
       </c>
       <c r="R2" t="n">
-        <v>6303353</v>
+        <v>6303292</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>121556504</v>
       </c>
       <c r="B3" t="n">
-        <v>90937</v>
+        <v>90945</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121556505</v>
+        <v>121556501</v>
       </c>
       <c r="B4" t="n">
-        <v>96372</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402925</v>
+        <v>402640</v>
       </c>
       <c r="R4" t="n">
-        <v>6303306</v>
+        <v>6302988</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121556501</v>
+        <v>121556505</v>
       </c>
       <c r="B5" t="n">
-        <v>5192</v>
+        <v>96380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>402640</v>
+        <v>402925</v>
       </c>
       <c r="R5" t="n">
-        <v>6302988</v>
+        <v>6303306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121556527</v>
+        <v>121556526</v>
       </c>
       <c r="B6" t="n">
-        <v>96372</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>402956</v>
+        <v>403015</v>
       </c>
       <c r="R6" t="n">
-        <v>6303292</v>
+        <v>6303353</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 26375-2022 artfynd.xlsx
+++ b/artfynd/A 26375-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121556505</v>
+        <v>121556501</v>
       </c>
       <c r="B2" t="n">
-        <v>96380</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402925</v>
+        <v>402640</v>
       </c>
       <c r="R2" t="n">
-        <v>6303306</v>
+        <v>6302988</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121556504</v>
+        <v>121556527</v>
       </c>
       <c r="B3" t="n">
-        <v>90945</v>
+        <v>96380</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1101</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402892</v>
+        <v>402956</v>
       </c>
       <c r="R3" t="n">
-        <v>6303180</v>
+        <v>6303292</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121556526</v>
+        <v>121556504</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>90945</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>1101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403015</v>
+        <v>402892</v>
       </c>
       <c r="R4" t="n">
-        <v>6303353</v>
+        <v>6303180</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121556527</v>
+        <v>121556505</v>
       </c>
       <c r="B5" t="n">
         <v>96380</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>402956</v>
+        <v>402925</v>
       </c>
       <c r="R5" t="n">
-        <v>6303292</v>
+        <v>6303306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121556501</v>
+        <v>121556526</v>
       </c>
       <c r="B6" t="n">
         <v>5193</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>402640</v>
+        <v>403015</v>
       </c>
       <c r="R6" t="n">
-        <v>6302988</v>
+        <v>6303353</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 26375-2022 artfynd.xlsx
+++ b/artfynd/A 26375-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121556501</v>
+        <v>121556505</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>96380</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402640</v>
+        <v>402925</v>
       </c>
       <c r="R2" t="n">
-        <v>6302988</v>
+        <v>6303306</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121556527</v>
+        <v>121556504</v>
       </c>
       <c r="B3" t="n">
-        <v>96380</v>
+        <v>90945</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>1101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402956</v>
+        <v>402892</v>
       </c>
       <c r="R3" t="n">
-        <v>6303292</v>
+        <v>6303180</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121556504</v>
+        <v>121556526</v>
       </c>
       <c r="B4" t="n">
-        <v>90945</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1101</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402892</v>
+        <v>403015</v>
       </c>
       <c r="R4" t="n">
-        <v>6303180</v>
+        <v>6303353</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121556505</v>
+        <v>121556527</v>
       </c>
       <c r="B5" t="n">
         <v>96380</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>402925</v>
+        <v>402956</v>
       </c>
       <c r="R5" t="n">
-        <v>6303306</v>
+        <v>6303292</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121556526</v>
+        <v>121556501</v>
       </c>
       <c r="B6" t="n">
         <v>5193</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>403015</v>
+        <v>402640</v>
       </c>
       <c r="R6" t="n">
-        <v>6303353</v>
+        <v>6302988</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 26375-2022 artfynd.xlsx
+++ b/artfynd/A 26375-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121556526</v>
+        <v>121556504</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>403015</v>
+        <v>402892</v>
       </c>
       <c r="R2" t="n">
-        <v>6303353</v>
+        <v>6303180</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,12 +779,7 @@
         <v>121556505</v>
       </c>
       <c r="B3" t="n">
-        <v>96380</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121556501</v>
+        <v>121556527</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402640</v>
+        <v>402956</v>
       </c>
       <c r="R4" t="n">
-        <v>6302988</v>
+        <v>6303292</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121556527</v>
+        <v>121556501</v>
       </c>
       <c r="B5" t="n">
-        <v>96380</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>402956</v>
+        <v>402640</v>
       </c>
       <c r="R5" t="n">
-        <v>6303292</v>
+        <v>6302988</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121556504</v>
+        <v>121556525</v>
       </c>
       <c r="B6" t="n">
-        <v>90945</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1101</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>402892</v>
+        <v>403181</v>
       </c>
       <c r="R6" t="n">
-        <v>6303180</v>
+        <v>6303438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,6 +1173,107 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>FNT0021 Gräshult</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121556526</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gräshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>403015</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6303353</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lidhult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>FNT0021 Gräshult</t>
         </is>

--- a/artfynd/A 26375-2022 artfynd.xlsx
+++ b/artfynd/A 26375-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>FNT0021 Gräshult</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121556504</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>FNT0021 Gräshult</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121556505</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>FNT0021 Gräshult</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121556527</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>FNT0021 Gräshult</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121556501</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>FNT0021 Gräshult</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121556525</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,8 +1308,21 @@
           <t>FNT0021 Gräshult</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121556526</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>